--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37571098-8783-4A56-9D7B-7E753EFC8C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7079A1C8-56F9-459E-BFBB-87B1B88D42D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="635" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="635" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="Nr8" sheetId="10" r:id="rId10"/>
     <sheet name="Nr9" sheetId="11" r:id="rId11"/>
     <sheet name="Nr10" sheetId="12" r:id="rId12"/>
+    <sheet name="Nr 11" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6115" uniqueCount="2597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6127" uniqueCount="2599">
   <si>
     <t>Imprint</t>
   </si>
@@ -7827,6 +7828,12 @@
   </si>
   <si>
     <t>Abeni har rättat issn, print och elektroniskt var ofta omkastat tidigare</t>
+  </si>
+  <si>
+    <t>2641-0397</t>
+  </si>
+  <si>
+    <t>Sexual and Reproductive Health Matters</t>
   </si>
 </sst>
 </file>
@@ -7899,12 +7906,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19818,7 +19824,7 @@
       <c r="D4" t="s">
         <v>2594</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" t="s">
         <v>2595</v>
       </c>
       <c r="F4" t="s">
@@ -19830,9 +19836,6 @@
       <c r="H4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -19848,6 +19851,59 @@
       </c>
       <c r="B8" t="s">
         <v>2590</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E5927D-A62C-4712-B778-F1899D84ED83}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="52.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2597</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2598</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/Tidskriftslistor_ändringar_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7079A1C8-56F9-459E-BFBB-87B1B88D42D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E81C4C6-450E-4394-BAE1-1DB258CA4107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="635" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="635" firstSheet="2" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan13" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="Nr9" sheetId="11" r:id="rId11"/>
     <sheet name="Nr10" sheetId="12" r:id="rId12"/>
     <sheet name="Nr 11" sheetId="13" r:id="rId13"/>
+    <sheet name="Nr 12" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6127" uniqueCount="2599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6310" uniqueCount="2676">
   <si>
     <t>Imprint</t>
   </si>
@@ -7834,6 +7835,237 @@
   </si>
   <si>
     <t>Sexual and Reproductive Health Matters</t>
+  </si>
+  <si>
+    <t>Hindawi</t>
+  </si>
+  <si>
+    <t>1365-2354</t>
+  </si>
+  <si>
+    <t>European Journal of Cancer Care</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/ejcc</t>
+  </si>
+  <si>
+    <t>1891-1803</t>
+  </si>
+  <si>
+    <t>Campbell Systematic Reviews</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/18911803</t>
+  </si>
+  <si>
+    <t>1618-2863</t>
+  </si>
+  <si>
+    <t>Engineering In Life Sciences</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/16182863</t>
+  </si>
+  <si>
+    <t>1439-0426</t>
+  </si>
+  <si>
+    <t>Journal of Applied Ichthyology</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/jai</t>
+  </si>
+  <si>
+    <t>2976-5501</t>
+  </si>
+  <si>
+    <t>Journal of GeoEnergy</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/jge</t>
+  </si>
+  <si>
+    <t>2642-3561</t>
+  </si>
+  <si>
+    <t>Liver Cancer International</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/26423561</t>
+  </si>
+  <si>
+    <t>1465-3435</t>
+  </si>
+  <si>
+    <t>0141-8211</t>
+  </si>
+  <si>
+    <t>European Journal Of Education</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/14653435</t>
+  </si>
+  <si>
+    <t>Flippar till OA</t>
+  </si>
+  <si>
+    <t>1099-145X</t>
+  </si>
+  <si>
+    <t>1085-3278</t>
+  </si>
+  <si>
+    <t>Land Degradation &amp; Development</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/1099145X</t>
+  </si>
+  <si>
+    <t>3066-9448</t>
+  </si>
+  <si>
+    <t>AgriFood: Journal of Agricultural Products for Food</t>
+  </si>
+  <si>
+    <t>https://iadns.onlinelibrary.wiley.com/journal/30669448</t>
+  </si>
+  <si>
+    <t>2994-1806</t>
+  </si>
+  <si>
+    <t>2994-1792</t>
+  </si>
+  <si>
+    <t>Barrier Immunity</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/29941806</t>
+  </si>
+  <si>
+    <t>3071-1096</t>
+  </si>
+  <si>
+    <t>Bioanalysis Advances</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/30711096</t>
+  </si>
+  <si>
+    <t>2996-2757</t>
+  </si>
+  <si>
+    <t>Food Biomacromolecules</t>
+  </si>
+  <si>
+    <t>https://iadns.onlinelibrary.wiley.com/journal/29962757</t>
+  </si>
+  <si>
+    <t>2995-5610</t>
+  </si>
+  <si>
+    <t>Energy Internet</t>
+  </si>
+  <si>
+    <t>https://ietresearch.onlinelibrary.wiley.com/journal/29952166</t>
+  </si>
+  <si>
+    <t>3065-9655</t>
+  </si>
+  <si>
+    <t>3065-9647</t>
+  </si>
+  <si>
+    <t>IET Smart Energy Systems</t>
+  </si>
+  <si>
+    <t>https://ietresearch.onlinelibrary.wiley.com/journal/30659655</t>
+  </si>
+  <si>
+    <t>2994-1393</t>
+  </si>
+  <si>
+    <t>Liver International Communications</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/29941393</t>
+  </si>
+  <si>
+    <t>3065-2731</t>
+  </si>
+  <si>
+    <t>Medicine Bulletin</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/30652731</t>
+  </si>
+  <si>
+    <t>3069-9711</t>
+  </si>
+  <si>
+    <t>MultiPsych</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/30699711</t>
+  </si>
+  <si>
+    <t>2994-9890</t>
+  </si>
+  <si>
+    <t>New Plant Protection</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/29949890</t>
+  </si>
+  <si>
+    <t>2994-175X</t>
+  </si>
+  <si>
+    <t>2994-1741</t>
+  </si>
+  <si>
+    <t>Organ Medicine</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/2994175x</t>
+  </si>
+  <si>
+    <t>3068-7306</t>
+  </si>
+  <si>
+    <t>Phytochemicals in Food and Medicine</t>
+  </si>
+  <si>
+    <t>https://iadns.onlinelibrary.wiley.com/journal/30687306</t>
+  </si>
+  <si>
+    <t>2997-6286</t>
+  </si>
+  <si>
+    <t>SCI Sustainability</t>
+  </si>
+  <si>
+    <t>https://scijournals.onlinelibrary.wiley.com/journal/29976286</t>
+  </si>
+  <si>
+    <t>2997-8874</t>
+  </si>
+  <si>
+    <t>Sensory Neuroscience</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/29978874</t>
+  </si>
+  <si>
+    <t>2998-1891</t>
+  </si>
+  <si>
+    <t>2998-4432</t>
+  </si>
+  <si>
+    <t>SmartBot</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/29981891</t>
   </si>
 </sst>
 </file>
@@ -7940,6 +8172,26 @@
     <tableColumn id="6" xr3:uid="{D2BB4442-BD64-4D7D-A782-CAFA127D7B25}" name="Publishing model"/>
     <tableColumn id="7" xr3:uid="{C200BD38-12D4-4EA4-A292-80FA41D2D3BF}" name="CC License options"/>
     <tableColumn id="8" xr3:uid="{A9C8E2CC-55E5-46C9-8471-6F11F6FDED2C}" name="Ändring"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BAE308A8-31E3-4BED-9BE3-08B039D4A253}" name="Table14" displayName="Table14" ref="A1:H25" totalsRowShown="0">
+  <autoFilter ref="A1:H25" xr:uid="{BAE308A8-31E3-4BED-9BE3-08B039D4A253}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H25">
+    <sortCondition ref="H1:H25"/>
+  </sortState>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{973B4DD9-10B5-44B8-ADC7-03C6E71CD101}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{810C5857-7628-4B36-BA7C-D9534E9E1E1B}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{02FBE1CC-596C-4DF4-9709-CE55E63D67AC}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{A300485B-6DA0-4345-B6E5-85F01AB19412}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{2C40E5DE-DCC6-465F-B0A4-63EBFB8451F8}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{38422386-D953-4F94-ACA6-5D88DD7E0326}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{83A6428E-80AF-4E3D-AC3B-6761971867E7}" name="CC License options"/>
+    <tableColumn id="8" xr3:uid="{7D03CB7A-E0D1-456B-9002-33F6DE5510FC}" name="Ändring"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -19911,6 +20163,622 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76FE6F77-9380-4E90-BE63-5F8198FDD130}">
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="46.5703125" customWidth="1"/>
+    <col min="8" max="8" width="24.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>593</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2599</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2600</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2601</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2602</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2604</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2605</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>611</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2607</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2608</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>593</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2599</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2610</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2613</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2614</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2615</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2616</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2617</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2618</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2619</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2620</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2621</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>593</v>
+      </c>
+      <c r="H9" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2623</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2624</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2625</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2626</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>593</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2627</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2628</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2629</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2630</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2631</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2632</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2633</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2634</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2635</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2636</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2638</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2639</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2641</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2642</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>593</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2643</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2644</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2645</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2646</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2647</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2648</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2649</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2650</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2651</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2652</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2653</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2654</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2655</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2656</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2657</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2658</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2661</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>593</v>
+      </c>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2663</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2664</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2665</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2666</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2667</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2668</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2669</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2673</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2674</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2675</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1D323B-A6AD-4330-BC48-B16F75806926}">
   <dimension ref="A1:H54"/>
